--- a/Modules/ImportGestionali/resources/samples/prodotti_gioielleria_test.xlsx
+++ b/Modules/ImportGestionali/resources/samples/prodotti_gioielleria_test.xlsx
@@ -60,9 +60,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetData>
-    <row r="1" spans="1:9" customHeight="0">
+    <row r="1" spans="1:10" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Codice</t>
@@ -75,7 +75,7 @@
       </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
-          <t>Nome</t>
+          <t>Nome IT</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
@@ -108,8 +108,13 @@
           <t>Taglia</t>
         </is>
       </c>
-    </row>
-    <row r="2" spans="1:9" customHeight="0">
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Nome EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:10" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
           <t>GIO-COLLANA-01</t>
@@ -140,8 +145,13 @@
           <t>attivo</t>
         </is>
       </c>
-    </row>
-    <row r="3" spans="1:9" customHeight="0">
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>Akoya Pearl Necklace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:10" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>AN-SOLIT-050-GIALLO</t>
@@ -183,7 +193,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:9" customHeight="0">
+    <row r="4" spans="1:10" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>AN-SOLIT-050-BIANCO</t>
@@ -220,7 +230,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:9" customHeight="0">
+    <row r="5" spans="1:10" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>AN-SOLITARIO</t>
@@ -241,8 +251,13 @@
           <t>attivo</t>
         </is>
       </c>
-    </row>
-    <row r="6" spans="1:9" customHeight="0">
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>Solitaire Ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:10" customHeight="0">
       <c r="A6" s="0" t="inlineStr">
         <is>
           <t>BR-TENNIS-M</t>
@@ -284,7 +299,7 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:9" customHeight="0">
+    <row r="7" spans="1:10" customHeight="0">
       <c r="A7" s="0" t="inlineStr">
         <is>
           <t>GIO-ORECC-02</t>
@@ -315,8 +330,13 @@
           <t>attivo</t>
         </is>
       </c>
-    </row>
-    <row r="8" spans="1:9" customHeight="0">
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Hoop Earrings</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:10" customHeight="0">
       <c r="A8" s="0" t="inlineStr">
         <is>
           <t>BR-TENNIS-S</t>
@@ -358,7 +378,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:9" customHeight="0">
+    <row r="9" spans="1:10" customHeight="0">
       <c r="A9" s="0" t="inlineStr">
         <is>
           <t>BR-TENNIS</t>
@@ -379,8 +399,13 @@
           <t>attivo</t>
         </is>
       </c>
-    </row>
-    <row r="10" spans="1:9" customHeight="0">
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Tennis Bracelet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:10" customHeight="0">
       <c r="A10" s="0" t="inlineStr">
         <is>
           <t>AN-SOLIT-070-GIALLO</t>
